--- a/ms_tables/tableS3_disparity_n8_E_small_fam.xlsx
+++ b/ms_tables/tableS3_disparity_n8_E_small_fam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thomas/Documents/GitHub/GvsP/ms_tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D57D96-0DB5-2840-957E-D860E01C5428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F291C101-3A1B-4548-8EE1-BD46DCA22EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37260" yWindow="1760" windowWidth="27320" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -650,6 +650,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -661,15 +670,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -698,8 +698,8 @@
       <xdr:rowOff>20600</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="219364" cy="175369"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -781,7 +781,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -841,7 +841,7 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>960119</xdr:colOff>
+      <xdr:colOff>953950</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>1960</xdr:rowOff>
     </xdr:from>
@@ -850,10 +850,10 @@
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
+            <xdr:cNvPr id="12" name="TextBox 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACCA9F40-71AB-B949-A9D2-B00109A400E5}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2208CD82-DE2C-E94B-B17D-0AE83DE6C714}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -861,7 +861,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4780279" y="205160"/>
+              <a:off x="4773021" y="201531"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -927,7 +927,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑔</m:t>
+                              <m:t>𝑝</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -985,7 +985,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑝</m:t>
+                              <m:t>𝑔</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -1002,10 +1002,10 @@
       <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
+            <xdr:cNvPr id="12" name="TextBox 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACCA9F40-71AB-B949-A9D2-B00109A400E5}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2208CD82-DE2C-E94B-B17D-0AE83DE6C714}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1013,7 +1013,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4780279" y="205160"/>
+              <a:off x="4773021" y="201531"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1052,37 +1052,37 @@
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔 ) ̂</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>  </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -1095,19 +1095,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>772700</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>771072</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>199571</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="606704" cy="204999"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="TextBox 3">
+            <xdr:cNvPr id="13" name="TextBox 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F296BE8-922B-2447-9A57-FE353DF2EB12}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EEF4F67-6CC6-B340-AB4E-07D8DB211D52}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1115,7 +1115,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2692940" y="203200"/>
+              <a:off x="2685143" y="199571"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1150,6 +1150,64 @@
                     <m:jc m:val="center"/>
                   </m:oMathParaPr>
                   <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̂"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑝</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:e>
+                    </m:acc>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>vs</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1181,62 +1239,10 @@
                       </a:rPr>
                       <m:t> </m:t>
                     </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:sty m:val="p"/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>vs</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̂"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:accPr>
-                      <m:e>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑟</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑝</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:acc>
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1244,10 +1250,10 @@
       <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="TextBox 3">
+            <xdr:cNvPr id="13" name="TextBox 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F296BE8-922B-2447-9A57-FE353DF2EB12}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EEF4F67-6CC6-B340-AB4E-07D8DB211D52}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1255,7 +1261,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2692940" y="203200"/>
+              <a:off x="2685143" y="199571"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1285,9 +1291,39 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔</a:t>
               </a:r>
               <a:r>
@@ -1296,25 +1332,7 @@
                 </a:rPr>
                 <a:t>  </a:t>
               </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1325,7 +1343,7 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>991111</xdr:colOff>
+      <xdr:colOff>989460</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>2583</xdr:rowOff>
     </xdr:from>
@@ -1334,10 +1352,10 @@
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="TextBox 4">
+            <xdr:cNvPr id="14" name="TextBox 13">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F5EE614-805A-204D-A10B-2801EFF1FE72}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8561788-F027-B840-9C23-B6F8CF38FA1C}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1345,7 +1363,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3734311" y="205783"/>
+              <a:off x="3729031" y="202154"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1480,10 +1498,10 @@
       <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="TextBox 4">
+            <xdr:cNvPr id="14" name="TextBox 13">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F5EE614-805A-204D-A10B-2801EFF1FE72}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8561788-F027-B840-9C23-B6F8CF38FA1C}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1491,7 +1509,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3734311" y="205783"/>
+              <a:off x="3729031" y="202154"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1573,7 +1591,7 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>949779</xdr:colOff>
+      <xdr:colOff>958304</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>1960</xdr:rowOff>
     </xdr:from>
@@ -1582,10 +1600,10 @@
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="TextBox 5">
+            <xdr:cNvPr id="15" name="TextBox 14">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE4B1D70-81FA-534C-A33F-8B5A7324E652}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15972CA1-D55F-C44C-B770-F3B666B5CA22}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1593,7 +1611,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="8356419" y="205160"/>
+              <a:off x="8369661" y="201531"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1659,7 +1677,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑔</m:t>
+                              <m:t>𝑝</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -1717,7 +1735,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑝</m:t>
+                              <m:t>𝑔</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -1734,10 +1752,10 @@
       <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="TextBox 5">
+            <xdr:cNvPr id="15" name="TextBox 14">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE4B1D70-81FA-534C-A33F-8B5A7324E652}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15972CA1-D55F-C44C-B770-F3B666B5CA22}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1745,7 +1763,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="8356419" y="205160"/>
+              <a:off x="8369661" y="201531"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1784,37 +1802,37 @@
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔 ) ̂</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>  </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -1827,19 +1845,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1363419</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>1383212</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>199571</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="606704" cy="204999"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="7" name="TextBox 6">
+            <xdr:cNvPr id="16" name="TextBox 15">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9481D031-45E7-0B4E-907C-62B57F52D29B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E10F52B2-670B-F046-9C38-37A72C5E114A}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1847,7 +1865,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6260539" y="203200"/>
+              <a:off x="6281783" y="199571"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -1882,6 +1900,64 @@
                     <m:jc m:val="center"/>
                   </m:oMathParaPr>
                   <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̂"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑝</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:e>
+                    </m:acc>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>vs</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1913,62 +1989,10 @@
                       </a:rPr>
                       <m:t> </m:t>
                     </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:sty m:val="p"/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>vs</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̂"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:accPr>
-                      <m:e>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑟</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑝</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:acc>
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1976,10 +2000,10 @@
       <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="7" name="TextBox 6">
+            <xdr:cNvPr id="16" name="TextBox 15">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9481D031-45E7-0B4E-907C-62B57F52D29B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E10F52B2-670B-F046-9C38-37A72C5E114A}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1987,7 +2011,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6260539" y="203200"/>
+              <a:off x="6281783" y="199571"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2017,9 +2041,39 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔</a:t>
               </a:r>
               <a:r>
@@ -2028,25 +2082,7 @@
                 </a:rPr>
                 <a:t>  </a:t>
               </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2057,7 +2093,7 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>980771</xdr:colOff>
+      <xdr:colOff>993814</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>2583</xdr:rowOff>
     </xdr:from>
@@ -2066,10 +2102,10 @@
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="8" name="TextBox 7">
+            <xdr:cNvPr id="17" name="TextBox 16">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7497CF75-A66E-5D43-8838-1202D0AB855E}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FA4621C-C2AE-0F48-9ED6-3914E900B7E4}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2077,7 +2113,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="7310451" y="205783"/>
+              <a:off x="7325671" y="202154"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2212,10 +2248,10 @@
       <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="8" name="TextBox 7">
+            <xdr:cNvPr id="17" name="TextBox 16">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7497CF75-A66E-5D43-8838-1202D0AB855E}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2FA4621C-C2AE-0F48-9ED6-3914E900B7E4}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2223,7 +2259,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="7310451" y="205783"/>
+              <a:off x="7325671" y="202154"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2305,7 +2341,7 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>945284</xdr:colOff>
+      <xdr:colOff>958304</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>1960</xdr:rowOff>
     </xdr:from>
@@ -2314,10 +2350,10 @@
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="9" name="TextBox 8">
+            <xdr:cNvPr id="18" name="TextBox 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B114B54A-964F-1B43-81B8-D9F8445F3A38}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2EE555A-065B-344A-8CBF-1ABAE8E046AA}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2325,7 +2361,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11907924" y="205160"/>
+              <a:off x="11925661" y="201531"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2391,7 +2427,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑔</m:t>
+                              <m:t>𝑝</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -2449,7 +2485,7 @@
                               <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
-                              <m:t>𝑝</m:t>
+                              <m:t>𝑔</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
@@ -2466,10 +2502,10 @@
       <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="9" name="TextBox 8">
+            <xdr:cNvPr id="18" name="TextBox 17">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B114B54A-964F-1B43-81B8-D9F8445F3A38}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2EE555A-065B-344A-8CBF-1ABAE8E046AA}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2477,7 +2513,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="11907924" y="205160"/>
+              <a:off x="11925661" y="201531"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2516,37 +2552,37 @@
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔 ) ̂</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>  </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="1" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t> </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -2559,19 +2595,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1352000</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>1355997</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>199571</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="606704" cy="204999"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="10" name="TextBox 9">
+            <xdr:cNvPr id="19" name="TextBox 18">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8D69958-43A9-8548-A186-CBF5F8CD8001}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{480E92E1-7484-7543-A075-2E1F569A124B}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2579,7 +2615,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9825440" y="203200"/>
+              <a:off x="9837783" y="199571"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2614,6 +2650,64 @@
                     <m:jc m:val="center"/>
                   </m:oMathParaPr>
                   <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:acc>
+                      <m:accPr>
+                        <m:chr m:val="̂"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:accPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑟</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑝</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                      </m:e>
+                    </m:acc>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
+                    <m:r>
+                      <m:rPr>
+                        <m:sty m:val="p"/>
+                      </m:rPr>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>vs</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="1" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t> </m:t>
+                    </m:r>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -2645,62 +2739,10 @@
                       </a:rPr>
                       <m:t> </m:t>
                     </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:sty m:val="p"/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>vs</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:acc>
-                      <m:accPr>
-                        <m:chr m:val="̂"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:accPr>
-                      <m:e>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑟</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑝</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:e>
-                    </m:acc>
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2708,10 +2750,10 @@
       <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="10" name="TextBox 9">
+            <xdr:cNvPr id="19" name="TextBox 18">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8D69958-43A9-8548-A186-CBF5F8CD8001}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{480E92E1-7484-7543-A075-2E1F569A124B}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2719,7 +2761,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9825440" y="203200"/>
+              <a:off x="9837783" y="199571"/>
               <a:ext cx="606704" cy="204999"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2749,9 +2791,39 @@
             <a:p>
               <a:pPr/>
               <a:r>
+                <a:rPr lang="en-US" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
+                <a:t>𝑟_𝑝 ) ̂</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>  </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>vs</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="1" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t> </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
                 <a:t>𝑟_𝑔</a:t>
               </a:r>
               <a:r>
@@ -2760,25 +2832,7 @@
                 </a:rPr>
                 <a:t>  </a:t>
               </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>vs </a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>(</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑟_𝑝 ) ̂</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
+              <a:endParaRPr lang="en-US" sz="1100" i="0"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -2789,7 +2843,7 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>976276</xdr:colOff>
+      <xdr:colOff>993814</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>2583</xdr:rowOff>
     </xdr:from>
@@ -2798,10 +2852,10 @@
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="11" name="TextBox 10">
+            <xdr:cNvPr id="20" name="TextBox 19">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BA8BB7C-FE9F-6C4C-AF69-2FC3F4B97F54}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B742151F-A3A2-934C-AC7B-39CE0BD91CF3}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2809,7 +2863,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10861956" y="205783"/>
+              <a:off x="10881671" y="202154"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -2944,10 +2998,10 @@
       <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="11" name="TextBox 10">
+            <xdr:cNvPr id="20" name="TextBox 19">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BA8BB7C-FE9F-6C4C-AF69-2FC3F4B97F54}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B742151F-A3A2-934C-AC7B-39CE0BD91CF3}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2955,7 +3009,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10861956" y="205783"/>
+              <a:off x="10881671" y="202154"/>
               <a:ext cx="707834" cy="181231"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3352,21 +3406,21 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="14" t="s">
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="14" t="s">
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
@@ -3387,10 +3441,10 @@
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="16">
+      <c r="A3" s="19">
         <v>0.1</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="19" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="3">
@@ -3425,8 +3479,8 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
       <c r="C4" s="5">
         <v>150</v>
       </c>
@@ -3459,8 +3513,8 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="16"/>
       <c r="C5" s="7">
         <v>500</v>
       </c>
@@ -3485,7 +3539,7 @@
       <c r="J5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="K5" s="12" t="s">
         <v>28</v>
       </c>
       <c r="L5" s="8" t="s">
@@ -3493,8 +3547,8 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
-      <c r="B6" s="16" t="s">
+      <c r="A6" s="15"/>
+      <c r="B6" s="19" t="s">
         <v>30</v>
       </c>
       <c r="C6" s="3">
@@ -3518,19 +3572,19 @@
       <c r="I6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="J6" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="K6" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="L6" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
       <c r="C7" s="5">
         <v>150</v>
       </c>
@@ -3543,7 +3597,7 @@
       <c r="F7" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="11" t="s">
         <v>43</v>
       </c>
       <c r="H7" s="6" t="s">
@@ -3552,19 +3606,19 @@
       <c r="I7" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="17" t="s">
+      <c r="J7" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="L7" s="17" t="s">
+      <c r="L7" s="11" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
       <c r="C8" s="7">
         <v>500</v>
       </c>
@@ -3577,7 +3631,7 @@
       <c r="F8" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="12" t="s">
         <v>52</v>
       </c>
       <c r="H8" s="8" t="s">
@@ -3586,19 +3640,19 @@
       <c r="I8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="J8" s="18" t="s">
+      <c r="J8" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="K8" s="18" t="s">
+      <c r="K8" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="18" t="s">
+      <c r="L8" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
-      <c r="B9" s="11" t="s">
+      <c r="A9" s="15"/>
+      <c r="B9" s="14" t="s">
         <v>58</v>
       </c>
       <c r="C9" s="5">
@@ -3633,8 +3687,8 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
       <c r="C10" s="5">
         <v>150</v>
       </c>
@@ -3667,8 +3721,8 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="5">
         <v>500</v>
       </c>
@@ -3693,7 +3747,7 @@
       <c r="J11" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="K11" s="12" t="s">
         <v>84</v>
       </c>
       <c r="L11" s="8" t="s">
@@ -3701,10 +3755,10 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="11">
+      <c r="A12" s="14">
         <v>0.5</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="19" t="s">
         <v>2</v>
       </c>
       <c r="C12" s="3">
@@ -3731,16 +3785,16 @@
       <c r="J12" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="K12" s="19" t="s">
+      <c r="K12" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="L12" s="19" t="s">
+      <c r="L12" s="13" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
       <c r="C13" s="5">
         <v>150</v>
       </c>
@@ -3765,16 +3819,16 @@
       <c r="J13" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="K13" s="17" t="s">
+      <c r="K13" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="L13" s="17" t="s">
+      <c r="L13" s="11" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
-      <c r="B14" s="13"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="16"/>
       <c r="C14" s="7">
         <v>500</v>
       </c>
@@ -3790,7 +3844,7 @@
       <c r="G14" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="H14" s="18" t="s">
+      <c r="H14" s="12" t="s">
         <v>108</v>
       </c>
       <c r="I14" s="8" t="s">
@@ -3799,7 +3853,7 @@
       <c r="J14" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="K14" s="18" t="s">
+      <c r="K14" s="12" t="s">
         <v>111</v>
       </c>
       <c r="L14" s="8" t="s">
@@ -3807,8 +3861,8 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
-      <c r="B15" s="16" t="s">
+      <c r="A15" s="15"/>
+      <c r="B15" s="19" t="s">
         <v>30</v>
       </c>
       <c r="C15" s="3">
@@ -3823,7 +3877,7 @@
       <c r="F15" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="13" t="s">
         <v>116</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -3832,19 +3886,19 @@
       <c r="I15" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="J15" s="19" t="s">
+      <c r="J15" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="K15" s="19" t="s">
+      <c r="K15" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="L15" s="19" t="s">
+      <c r="L15" s="13" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
       <c r="C16" s="5">
         <v>150</v>
       </c>
@@ -3857,7 +3911,7 @@
       <c r="F16" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="G16" s="17" t="s">
+      <c r="G16" s="11" t="s">
         <v>125</v>
       </c>
       <c r="H16" s="6" t="s">
@@ -3866,19 +3920,19 @@
       <c r="I16" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="J16" s="17" t="s">
+      <c r="J16" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="K16" s="17" t="s">
+      <c r="K16" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="L16" s="17" t="s">
+      <c r="L16" s="11" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
-      <c r="B17" s="13"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="16"/>
       <c r="C17" s="7">
         <v>500</v>
       </c>
@@ -3891,28 +3945,28 @@
       <c r="F17" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="G17" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="H17" s="18" t="s">
+      <c r="H17" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="I17" s="18" t="s">
+      <c r="I17" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="J17" s="18" t="s">
+      <c r="J17" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="K17" s="18" t="s">
+      <c r="K17" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="L17" s="18" t="s">
+      <c r="L17" s="12" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
-      <c r="B18" s="11" t="s">
+      <c r="A18" s="15"/>
+      <c r="B18" s="14" t="s">
         <v>58</v>
       </c>
       <c r="C18" s="5">
@@ -3939,7 +3993,7 @@
       <c r="J18" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="K18" s="17" t="s">
+      <c r="K18" s="11" t="s">
         <v>147</v>
       </c>
       <c r="L18" s="6" t="s">
@@ -3947,8 +4001,8 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
       <c r="C19" s="5">
         <v>150</v>
       </c>
@@ -3973,16 +4027,16 @@
       <c r="J19" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="K19" s="17" t="s">
+      <c r="K19" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="L19" s="17" t="s">
+      <c r="L19" s="11" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
       <c r="C20" s="7">
         <v>500</v>
       </c>
@@ -3998,7 +4052,7 @@
       <c r="G20" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="H20" s="18" t="s">
+      <c r="H20" s="12" t="s">
         <v>162</v>
       </c>
       <c r="I20" s="8" t="s">
@@ -4007,10 +4061,10 @@
       <c r="J20" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="K20" s="18" t="s">
+      <c r="K20" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="L20" s="18" t="s">
+      <c r="L20" s="12" t="s">
         <v>166</v>
       </c>
     </row>
